--- a/src/main/resources/testdata/LoginData.xlsx
+++ b/src/main/resources/testdata/LoginData.xlsx
@@ -45,7 +45,7 @@
     <t>Epic sadface: Sorry, this user has been locked out.</t>
   </si>
   <si>
-    <t>Epic sadface: Username and password do not match any user in this service.</t>
+    <t>Epic sadface: Username and password do not match any user in this service</t>
   </si>
 </sst>
 </file>
